--- a/template/RDO.xlsx
+++ b/template/RDO.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorio\Gerar_Relatorio\template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EA3844-0D31-41F1-95F8-6C79A23E6F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-38510" yWindow="-6550" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" 2026-01-01" sheetId="2" r:id="rId1"/>
@@ -12,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">' 2026-01-01'!$B$1:$K$78</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterate="1" iterateDelta="0.01"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="0.01"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Jaime Hernández</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -71,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -114,7 +120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -190,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -223,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -289,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0">
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -322,7 +328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -355,7 +361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0">
+    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -388,7 +394,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -421,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G50" authorId="0">
+    <comment ref="G50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -445,7 +451,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C62" authorId="0">
+    <comment ref="C62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -478,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G62" authorId="0">
+    <comment ref="G62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -511,7 +517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J69" authorId="0">
+    <comment ref="J69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -544,7 +550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C71" authorId="0">
+    <comment ref="C71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -577,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D71" authorId="0">
+    <comment ref="D71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -610,7 +616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -643,7 +649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J71" authorId="0">
+    <comment ref="J71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -676,7 +682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C74" authorId="0">
+    <comment ref="C74" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -709,7 +715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D74" authorId="0">
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -887,7 +893,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dddd"/>
     <numFmt numFmtId="165" formatCode="[h]:mm"/>
@@ -1899,7 +1905,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1994,6 +2000,210 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="18" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2003,59 +2213,119 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="18" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="18" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="18" fillId="0" borderId="64" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="23" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2064,15 +2334,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="23" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2088,277 +2349,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="24" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="18" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="18" fillId="0" borderId="64" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="67" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="47" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="57" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2393,7 +2390,7 @@
         <xdr:cNvPr id="2" name="Line 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9401838C-3BB7-4068-B5C0-E5180C178607}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9401838C-3BB7-4068-B5C0-E5180C178607}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2441,10 +2438,10 @@
         <xdr:cNvPr id="3" name="Line 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9E4062-0CE8-4151-AE53-DA887599911C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EA79C897-4CF1-4FFA-8E9C-1653E7947850}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9E4062-0CE8-4151-AE53-DA887599911C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EA79C897-4CF1-4FFA-8E9C-1653E7947850}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2492,10 +2489,10 @@
         <xdr:cNvPr id="4" name="Line 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BBF9BC3-6AD4-4E6F-92FC-E1129252DF59}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{AA51D6AE-5BC6-43C3-8DE8-3C60825007DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BBF9BC3-6AD4-4E6F-92FC-E1129252DF59}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{AA51D6AE-5BC6-43C3-8DE8-3C60825007DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2543,10 +2540,10 @@
         <xdr:cNvPr id="5" name="Line 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC032D8B-ABCF-444D-8191-56A60CEFE8B5}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BDFC6E08-E903-4C03-884D-CC7AE57F55B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC032D8B-ABCF-444D-8191-56A60CEFE8B5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BDFC6E08-E903-4C03-884D-CC7AE57F55B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2594,10 +2591,10 @@
         <xdr:cNvPr id="6" name="Line 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E20BA9B7-7893-4D84-867B-8BE5A96D3FA7}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DB678817-A6CD-4FA1-AA5A-AEEDDC44A628}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E20BA9B7-7893-4D84-867B-8BE5A96D3FA7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DB678817-A6CD-4FA1-AA5A-AEEDDC44A628}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2645,10 +2642,10 @@
         <xdr:cNvPr id="7" name="Line 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53BD1017-A77A-493B-8A72-D6036250C0CA}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F8CEA373-BB0D-419E-AEEF-C337D6FD6F3B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53BD1017-A77A-493B-8A72-D6036250C0CA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F8CEA373-BB0D-419E-AEEF-C337D6FD6F3B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2696,10 +2693,10 @@
         <xdr:cNvPr id="8" name="Line 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB3560C0-04EF-402F-9A90-15CFFFEB4ADB}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{669C938B-BB52-447B-8442-D3704AEFCE68}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB3560C0-04EF-402F-9A90-15CFFFEB4ADB}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{669C938B-BB52-447B-8442-D3704AEFCE68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2747,10 +2744,10 @@
         <xdr:cNvPr id="9" name="Line 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB8432A5-DB62-4C8F-BB78-1BBD14556300}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D15D193-48DB-43C3-AE9C-95143345D990}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB8432A5-DB62-4C8F-BB78-1BBD14556300}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D15D193-48DB-43C3-AE9C-95143345D990}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2798,10 +2795,10 @@
         <xdr:cNvPr id="10" name="Line 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E92B4A5-5A4E-4A25-89B6-5EC603ACD2D9}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{506BC451-B9CF-430F-979B-46B332A782D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E92B4A5-5A4E-4A25-89B6-5EC603ACD2D9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{506BC451-B9CF-430F-979B-46B332A782D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2849,10 +2846,10 @@
         <xdr:cNvPr id="11" name="Line 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C662409-C1FA-4C6B-9D63-1CC6375CC922}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E78D294B-6D44-44AA-A45B-483DA6D22B82}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C662409-C1FA-4C6B-9D63-1CC6375CC922}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E78D294B-6D44-44AA-A45B-483DA6D22B82}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2900,10 +2897,10 @@
         <xdr:cNvPr id="12" name="Line 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F9AE50D-C3D2-4D8A-97F7-85216900C764}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{06D1F03F-0CF9-47C0-8C1F-80D59E979F57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F9AE50D-C3D2-4D8A-97F7-85216900C764}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{06D1F03F-0CF9-47C0-8C1F-80D59E979F57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2951,10 +2948,10 @@
         <xdr:cNvPr id="13" name="Line 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C49DF68-E4BE-4A75-93B6-54527E9DE01B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CB66B906-36D2-40B3-A53D-FFF3CA204A52}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C49DF68-E4BE-4A75-93B6-54527E9DE01B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CB66B906-36D2-40B3-A53D-FFF3CA204A52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3002,10 +2999,10 @@
         <xdr:cNvPr id="14" name="Line 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A09DFDE-9E43-42AE-A3C6-A032E64A5A74}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A973C6BE-28C4-4651-9F3F-49D5A055BDED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A09DFDE-9E43-42AE-A3C6-A032E64A5A74}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A973C6BE-28C4-4651-9F3F-49D5A055BDED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3053,10 +3050,10 @@
         <xdr:cNvPr id="15" name="Line 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ECF90AC-3170-48F5-B401-0CDEBF522200}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{89AEF9EA-54B7-4A00-A9EA-78EB5440AB11}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ECF90AC-3170-48F5-B401-0CDEBF522200}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{89AEF9EA-54B7-4A00-A9EA-78EB5440AB11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3104,10 +3101,10 @@
         <xdr:cNvPr id="16" name="Line 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4515580-C4F8-45E2-ADB3-068E3EB9B11B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8FA3D063-3B65-4DF5-917B-59BBFCFDBB98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4515580-C4F8-45E2-ADB3-068E3EB9B11B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8FA3D063-3B65-4DF5-917B-59BBFCFDBB98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3155,10 +3152,10 @@
         <xdr:cNvPr id="17" name="Line 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E160CBC1-5925-41D7-B031-33BA9A2A2C78}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D8C47720-D748-4218-9997-B33CA9BAEBC6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E160CBC1-5925-41D7-B031-33BA9A2A2C78}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D8C47720-D748-4218-9997-B33CA9BAEBC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3206,10 +3203,10 @@
         <xdr:cNvPr id="18" name="Line 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBB1AC8-D5BC-4EB8-A167-A68A9BE3B959}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{61877CE1-9F80-4647-B3AC-A7571BCD8A19}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBB1AC8-D5BC-4EB8-A167-A68A9BE3B959}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{61877CE1-9F80-4647-B3AC-A7571BCD8A19}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3257,10 +3254,10 @@
         <xdr:cNvPr id="19" name="Line 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5DE6CC-1E56-409A-967B-7DF8B1A09628}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3F9C4A9F-9FE3-4AEC-B81E-E045077795CD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5DE6CC-1E56-409A-967B-7DF8B1A09628}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3F9C4A9F-9FE3-4AEC-B81E-E045077795CD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3308,10 +3305,10 @@
         <xdr:cNvPr id="20" name="Line 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80023BC4-8287-48AB-87A4-2B5727C4BEFA}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1D6AD68B-6F86-4F33-9F90-E449C5F9D973}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80023BC4-8287-48AB-87A4-2B5727C4BEFA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1D6AD68B-6F86-4F33-9F90-E449C5F9D973}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3359,10 +3356,10 @@
         <xdr:cNvPr id="21" name="Line 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE62496-4269-4644-BB5A-F8FFEE3C8020}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{73390F05-56A8-4904-A474-5746488A154C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE62496-4269-4644-BB5A-F8FFEE3C8020}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{73390F05-56A8-4904-A474-5746488A154C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3410,10 +3407,10 @@
         <xdr:cNvPr id="22" name="Line 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9EE105-FE61-4BB3-9EAA-35BFFCB7312E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E836DAB6-C7BC-45D7-8E22-B274C1A7C141}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9EE105-FE61-4BB3-9EAA-35BFFCB7312E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E836DAB6-C7BC-45D7-8E22-B274C1A7C141}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3461,10 +3458,10 @@
         <xdr:cNvPr id="23" name="Line 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEB4A366-7FBD-47C6-BC17-49A8DC757630}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{41F5ADD0-22BC-40A2-A932-DC669373ADC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEB4A366-7FBD-47C6-BC17-49A8DC757630}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{41F5ADD0-22BC-40A2-A932-DC669373ADC8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3512,10 +3509,10 @@
         <xdr:cNvPr id="24" name="Line 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{801B1319-E0C2-4A36-B842-95D1E85A7CD2}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A534FEB5-2137-4C54-BF4E-7359BD34B54E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{801B1319-E0C2-4A36-B842-95D1E85A7CD2}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A534FEB5-2137-4C54-BF4E-7359BD34B54E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3563,10 +3560,10 @@
         <xdr:cNvPr id="25" name="Line 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7A143DB-8CF4-4785-841A-62AB5C4BECDB}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1EF4BBE4-EC81-4920-B2D8-2CC480848F89}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7A143DB-8CF4-4785-841A-62AB5C4BECDB}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1EF4BBE4-EC81-4920-B2D8-2CC480848F89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3614,10 +3611,10 @@
         <xdr:cNvPr id="26" name="Line 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E470D55C-F8AC-4686-9990-6D027D0F9D22}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E3F1F467-B05E-48B2-8533-AA18CB16E5A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E470D55C-F8AC-4686-9990-6D027D0F9D22}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E3F1F467-B05E-48B2-8533-AA18CB16E5A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3665,10 +3662,10 @@
         <xdr:cNvPr id="27" name="Line 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28DA593D-3205-4599-A454-E2EFDCA6BF65}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5971F89C-AB8E-4E5B-A73C-C8DE65165BDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28DA593D-3205-4599-A454-E2EFDCA6BF65}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5971F89C-AB8E-4E5B-A73C-C8DE65165BDD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3716,10 +3713,10 @@
         <xdr:cNvPr id="28" name="Line 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD73FF9E-B8CC-4441-A445-2B1C170BD884}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D496605D-EED6-48DC-98B0-131E372154F0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD73FF9E-B8CC-4441-A445-2B1C170BD884}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D496605D-EED6-48DC-98B0-131E372154F0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3767,10 +3764,10 @@
         <xdr:cNvPr id="29" name="Line 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AC0CD1F-1599-40AF-8C45-54475A780B4E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CBA462BB-7F3B-4ECA-B1A9-C782D8E5BB56}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AC0CD1F-1599-40AF-8C45-54475A780B4E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{CBA462BB-7F3B-4ECA-B1A9-C782D8E5BB56}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3818,10 +3815,10 @@
         <xdr:cNvPr id="30" name="Line 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C19FFC37-3C68-4F5D-A593-0A901E0C7C55}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{372C119E-2911-4FAA-9FAB-AA471DF4CA98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C19FFC37-3C68-4F5D-A593-0A901E0C7C55}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{372C119E-2911-4FAA-9FAB-AA471DF4CA98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3869,10 +3866,10 @@
         <xdr:cNvPr id="31" name="Line 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{677F24E3-2572-4331-AAEF-62B9FAD0C101}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8BF4E609-601B-4E71-8E9E-30B605A005E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{677F24E3-2572-4331-AAEF-62B9FAD0C101}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8BF4E609-601B-4E71-8E9E-30B605A005E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3920,10 +3917,10 @@
         <xdr:cNvPr id="32" name="Line 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94CD35CC-515F-48C6-A59B-8C511183DC78}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4D9C6BF0-F5EC-4C1C-8335-B9269213CA60}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94CD35CC-515F-48C6-A59B-8C511183DC78}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4D9C6BF0-F5EC-4C1C-8335-B9269213CA60}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3971,10 +3968,10 @@
         <xdr:cNvPr id="33" name="Line 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F102ED7B-DA54-42E4-AA6B-803BD77909E1}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5DE6639E-CBCA-4199-870E-A6609EF9E8BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F102ED7B-DA54-42E4-AA6B-803BD77909E1}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5DE6639E-CBCA-4199-870E-A6609EF9E8BC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4022,10 +4019,10 @@
         <xdr:cNvPr id="34" name="Line 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C6DEB0-9468-4270-AB3C-9BED801946BA}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2023DB1F-01A2-4992-994E-D21BA7A55ECD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4C6DEB0-9468-4270-AB3C-9BED801946BA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2023DB1F-01A2-4992-994E-D21BA7A55ECD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4073,10 +4070,10 @@
         <xdr:cNvPr id="35" name="Line 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF16E3C5-5003-42AC-AAF1-FADA1D6E689B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D7398B97-99DF-4C05-B76E-44B2542E0260}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF16E3C5-5003-42AC-AAF1-FADA1D6E689B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D7398B97-99DF-4C05-B76E-44B2542E0260}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4124,10 +4121,10 @@
         <xdr:cNvPr id="36" name="Line 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04F7DAF3-7390-490A-AB4B-7FB6BADE49DA}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{24B54D32-C859-4885-879B-4DC51F9BEAD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04F7DAF3-7390-490A-AB4B-7FB6BADE49DA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{24B54D32-C859-4885-879B-4DC51F9BEAD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4175,10 +4172,10 @@
         <xdr:cNvPr id="37" name="Line 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE0B5DC8-CF7A-4F3E-AD82-5B152A75D509}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F8268492-519C-4FE8-8281-1BE585253DEE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE0B5DC8-CF7A-4F3E-AD82-5B152A75D509}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F8268492-519C-4FE8-8281-1BE585253DEE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4226,10 +4223,10 @@
         <xdr:cNvPr id="38" name="Line 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31974B8-6075-4048-A448-A22EC1B4199E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7EF266A7-47EA-4B3B-BFE5-7D4012634EBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31974B8-6075-4048-A448-A22EC1B4199E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7EF266A7-47EA-4B3B-BFE5-7D4012634EBD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4277,10 +4274,10 @@
         <xdr:cNvPr id="39" name="Line 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06D7117A-B174-4C3D-AABE-12E3F770A49E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{512999A9-07BE-4C4D-8A77-6D435604FA4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06D7117A-B174-4C3D-AABE-12E3F770A49E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{512999A9-07BE-4C4D-8A77-6D435604FA4F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4328,10 +4325,10 @@
         <xdr:cNvPr id="40" name="Line 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7F6592B-BF97-4017-ABF7-EE19241B2B9D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0349752F-F46C-4E3B-B14B-5D36A672D9EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7F6592B-BF97-4017-ABF7-EE19241B2B9D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0349752F-F46C-4E3B-B14B-5D36A672D9EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4379,10 +4376,10 @@
         <xdr:cNvPr id="41" name="Line 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD8BD678-A54A-465D-967A-7EDAD6500D6D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{FDB02477-FAFE-4121-B0E9-05E88EDABED4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD8BD678-A54A-465D-967A-7EDAD6500D6D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{FDB02477-FAFE-4121-B0E9-05E88EDABED4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4430,10 +4427,10 @@
         <xdr:cNvPr id="42" name="Line 41">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DCA3DF-87B6-4231-B557-2A936588A1DE}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C2C54C1C-4060-4794-A439-2B3B8B94E856}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2DCA3DF-87B6-4231-B557-2A936588A1DE}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C2C54C1C-4060-4794-A439-2B3B8B94E856}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4481,10 +4478,10 @@
         <xdr:cNvPr id="43" name="Line 42">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0B8057F-0A9C-46CD-B59D-2FB15B400B75}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C9DB0CD8-7EDF-488E-836E-756F38B58CB0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0B8057F-0A9C-46CD-B59D-2FB15B400B75}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C9DB0CD8-7EDF-488E-836E-756F38B58CB0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4532,10 +4529,10 @@
         <xdr:cNvPr id="44" name="Line 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBE3667-CB10-4029-AB7A-5193FBC1E49D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6192D26E-042E-4A62-BC92-3921734A61AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CBE3667-CB10-4029-AB7A-5193FBC1E49D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6192D26E-042E-4A62-BC92-3921734A61AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4583,10 +4580,10 @@
         <xdr:cNvPr id="45" name="Line 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABECE3D1-F9AB-4C05-A32B-F4C67D4A7B8D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7FB2E222-3404-4B73-8E7B-7138634E5037}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABECE3D1-F9AB-4C05-A32B-F4C67D4A7B8D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7FB2E222-3404-4B73-8E7B-7138634E5037}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4634,10 +4631,10 @@
         <xdr:cNvPr id="46" name="Line 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D68C846-8AEC-440B-9456-D53FDB6F8E6B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0B7B876F-115F-4CF5-99A8-CCFF16246DDC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D68C846-8AEC-440B-9456-D53FDB6F8E6B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0B7B876F-115F-4CF5-99A8-CCFF16246DDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4685,10 +4682,10 @@
         <xdr:cNvPr id="47" name="Line 46">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28D31143-8F5D-4A40-9F42-4FA99BD37391}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6E662F2D-C743-4C35-99D4-DD4949EB474C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28D31143-8F5D-4A40-9F42-4FA99BD37391}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6E662F2D-C743-4C35-99D4-DD4949EB474C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4736,10 +4733,10 @@
         <xdr:cNvPr id="48" name="Line 47">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB75E44A-059A-408A-810B-4FB3FA10030E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B41C9A40-48E6-42E5-B695-7F4E93FCE9B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB75E44A-059A-408A-810B-4FB3FA10030E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B41C9A40-48E6-42E5-B695-7F4E93FCE9B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4787,10 +4784,10 @@
         <xdr:cNvPr id="49" name="Line 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38814B12-37CC-45A5-982D-21F078D432A2}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{552EDE22-3012-4396-8DA7-D2B37E754AC5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38814B12-37CC-45A5-982D-21F078D432A2}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{552EDE22-3012-4396-8DA7-D2B37E754AC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4838,10 +4835,10 @@
         <xdr:cNvPr id="50" name="Line 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A67EE44C-3914-437C-9B77-5D41DBF721EC}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45D172E6-2604-4771-93E9-4744B2C77A7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A67EE44C-3914-437C-9B77-5D41DBF721EC}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45D172E6-2604-4771-93E9-4744B2C77A7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4889,10 +4886,10 @@
         <xdr:cNvPr id="51" name="Line 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23483EF1-432D-4F2E-BBFD-9020F4DFC4EE}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4EB5AC03-E473-4281-916B-0A11B370075E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23483EF1-432D-4F2E-BBFD-9020F4DFC4EE}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4EB5AC03-E473-4281-916B-0A11B370075E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4940,10 +4937,10 @@
         <xdr:cNvPr id="52" name="Line 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28C50B35-03B7-4B81-9C7E-A3CD1C4315C0}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F0577E7D-0943-4903-A302-3F2DC3322B3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28C50B35-03B7-4B81-9C7E-A3CD1C4315C0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F0577E7D-0943-4903-A302-3F2DC3322B3A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4991,10 +4988,10 @@
         <xdr:cNvPr id="53" name="Line 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0C2489A-A461-4649-BC75-4C4ED21C3728}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8ABE9322-ED8C-4CF2-819B-0431DAABF1B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0C2489A-A461-4649-BC75-4C4ED21C3728}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8ABE9322-ED8C-4CF2-819B-0431DAABF1B1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5042,10 +5039,10 @@
         <xdr:cNvPr id="54" name="Line 53">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1D8AAB-D5E9-4704-B67D-E61C619D4883}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C2425963-5388-4BE7-B30F-F336916323E6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B1D8AAB-D5E9-4704-B67D-E61C619D4883}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C2425963-5388-4BE7-B30F-F336916323E6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5093,10 +5090,10 @@
         <xdr:cNvPr id="55" name="Line 54">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C005ABA-068E-468C-B2EA-B5002ADE6A65}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7B800028-6C62-4AB7-9EF3-FE8C2F7F31E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C005ABA-068E-468C-B2EA-B5002ADE6A65}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7B800028-6C62-4AB7-9EF3-FE8C2F7F31E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5144,10 +5141,10 @@
         <xdr:cNvPr id="56" name="Line 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82B424D8-D45A-412B-B034-07BAAC18D76C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{08C29BDE-AAA0-448F-9B8B-997B386F0188}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82B424D8-D45A-412B-B034-07BAAC18D76C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{08C29BDE-AAA0-448F-9B8B-997B386F0188}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5195,10 +5192,10 @@
         <xdr:cNvPr id="57" name="Line 56">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00F36E90-5A96-481B-B872-7FDA522D3F6E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B712C0EF-CF3A-4A0F-B2C7-A295E9C3877C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00F36E90-5A96-481B-B872-7FDA522D3F6E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B712C0EF-CF3A-4A0F-B2C7-A295E9C3877C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5246,10 +5243,10 @@
         <xdr:cNvPr id="58" name="Line 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6322E1D2-0369-4A57-AB2D-560DC51398BA}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B8A3F51F-003A-46CE-84B0-CCC2B19BD3F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6322E1D2-0369-4A57-AB2D-560DC51398BA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B8A3F51F-003A-46CE-84B0-CCC2B19BD3F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5297,10 +5294,10 @@
         <xdr:cNvPr id="59" name="Line 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79FF2A62-1549-4A99-A6D5-608844249B5B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{60DA32AC-723A-42F6-8475-7F6F03C831B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79FF2A62-1549-4A99-A6D5-608844249B5B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{60DA32AC-723A-42F6-8475-7F6F03C831B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5348,10 +5345,10 @@
         <xdr:cNvPr id="60" name="Line 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E6FC70-F0AD-49C4-8FDB-C633330AF2B6}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F819B37E-A88E-485A-88E9-4C964D7A8AFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94E6FC70-F0AD-49C4-8FDB-C633330AF2B6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F819B37E-A88E-485A-88E9-4C964D7A8AFA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5399,10 +5396,10 @@
         <xdr:cNvPr id="61" name="Line 60">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1269EE-CE65-4461-A6AA-618983E14CC4}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BFD0BB91-6338-49E6-8E90-04F79C2299AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1269EE-CE65-4461-A6AA-618983E14CC4}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BFD0BB91-6338-49E6-8E90-04F79C2299AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5450,10 +5447,10 @@
         <xdr:cNvPr id="62" name="Line 61">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{734A54B5-25A0-4DF4-A8EC-11E42A2A4758}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0F63AF7F-94C3-4A83-8460-2F62B3938F84}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{734A54B5-25A0-4DF4-A8EC-11E42A2A4758}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0F63AF7F-94C3-4A83-8460-2F62B3938F84}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5501,10 +5498,10 @@
         <xdr:cNvPr id="63" name="Line 62">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8843825-718D-4C2E-8749-68CF0448AEA2}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{27E6EFDF-A812-4FC4-AE18-9FD90FA38C22}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8843825-718D-4C2E-8749-68CF0448AEA2}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{27E6EFDF-A812-4FC4-AE18-9FD90FA38C22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5552,10 +5549,10 @@
         <xdr:cNvPr id="64" name="Line 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6BBE7A7-5DC0-4260-8EBD-F6552ECAEAE6}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EB7454D3-1EA9-4B3F-9B22-23BAE3F535F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6BBE7A7-5DC0-4260-8EBD-F6552ECAEAE6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EB7454D3-1EA9-4B3F-9B22-23BAE3F535F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5603,10 +5600,10 @@
         <xdr:cNvPr id="65" name="Line 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB6D845-8190-415F-A93F-C9E93098FB59}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{150D504C-BCC6-4394-9547-613BAF236A45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB6D845-8190-415F-A93F-C9E93098FB59}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{150D504C-BCC6-4394-9547-613BAF236A45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5654,10 +5651,10 @@
         <xdr:cNvPr id="66" name="Line 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA1CDD1-EEF3-4976-9EA1-C44BB33D8E23}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{47356131-2661-4A74-9EC0-68DA28D8E2EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA1CDD1-EEF3-4976-9EA1-C44BB33D8E23}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{47356131-2661-4A74-9EC0-68DA28D8E2EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5705,10 +5702,10 @@
         <xdr:cNvPr id="67" name="Line 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AC09E54-0B78-4DD2-B787-D30EBE7B7D61}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD40B3D2-10A6-4FC1-B7BE-800E0F164C07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AC09E54-0B78-4DD2-B787-D30EBE7B7D61}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DD40B3D2-10A6-4FC1-B7BE-800E0F164C07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5756,10 +5753,10 @@
         <xdr:cNvPr id="68" name="Line 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11565142-43A9-4A13-B062-147D7039A5C9}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{507A8CBE-901A-47E0-9A89-6698F46C5110}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11565142-43A9-4A13-B062-147D7039A5C9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{507A8CBE-901A-47E0-9A89-6698F46C5110}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5807,10 +5804,10 @@
         <xdr:cNvPr id="69" name="Line 68">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6679EB3-18D2-4E5F-98AC-B7CC5E4FB244}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D20DE4E-4E0E-4E32-8752-04722623E5A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6679EB3-18D2-4E5F-98AC-B7CC5E4FB244}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D20DE4E-4E0E-4E32-8752-04722623E5A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5858,10 +5855,10 @@
         <xdr:cNvPr id="70" name="Line 69">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4F52695-5DE4-44FD-8667-AFE0089F539F}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9420603A-6E56-45C7-900C-0A530FA848A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4F52695-5DE4-44FD-8667-AFE0089F539F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9420603A-6E56-45C7-900C-0A530FA848A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5909,10 +5906,10 @@
         <xdr:cNvPr id="71" name="Line 70">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{748F713D-9E64-4CB2-A3F5-729B45FAE58D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{26FB115F-7DF5-47EE-8AE5-FE62166B406E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{748F713D-9E64-4CB2-A3F5-729B45FAE58D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{26FB115F-7DF5-47EE-8AE5-FE62166B406E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5960,10 +5957,10 @@
         <xdr:cNvPr id="72" name="Line 71">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFD392B-7332-4353-AFA6-31D57FFFA35C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8F571793-701A-447B-98CE-6B01B81BE688}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBFD392B-7332-4353-AFA6-31D57FFFA35C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8F571793-701A-447B-98CE-6B01B81BE688}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6011,10 +6008,10 @@
         <xdr:cNvPr id="73" name="Line 72">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{140DB698-CBBC-43E8-A1BC-1ED61BE9F321}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8DE89E55-ABA6-48B9-9A68-EB43CD95B094}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{140DB698-CBBC-43E8-A1BC-1ED61BE9F321}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8DE89E55-ABA6-48B9-9A68-EB43CD95B094}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6062,10 +6059,10 @@
         <xdr:cNvPr id="74" name="Line 73">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615600FD-FFCB-4321-8AFB-AD97C905C08A}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3540D069-B0F8-47DF-9DD5-A9772AAC8EC5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{615600FD-FFCB-4321-8AFB-AD97C905C08A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3540D069-B0F8-47DF-9DD5-A9772AAC8EC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6113,10 +6110,10 @@
         <xdr:cNvPr id="75" name="Line 74">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D95FDA8-0AFE-44A2-AEDB-F69DF8275948}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C68873D4-990D-4112-9D48-0226063ECDE1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D95FDA8-0AFE-44A2-AEDB-F69DF8275948}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C68873D4-990D-4112-9D48-0226063ECDE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6164,10 +6161,10 @@
         <xdr:cNvPr id="76" name="Line 75">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E954D6-FBE3-411A-ACCD-6F9E2639EE3C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D1131DC-5DBC-41A9-B578-DE67800B46B0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E954D6-FBE3-411A-ACCD-6F9E2639EE3C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3D1131DC-5DBC-41A9-B578-DE67800B46B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6215,10 +6212,10 @@
         <xdr:cNvPr id="77" name="Line 76">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9280D32C-7910-4CBE-B561-B3B859D0564E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5DF04B31-198A-460A-97AF-DC909C7DE7BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9280D32C-7910-4CBE-B561-B3B859D0564E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5DF04B31-198A-460A-97AF-DC909C7DE7BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6266,10 +6263,10 @@
         <xdr:cNvPr id="78" name="Line 77">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E2291D4-560B-4FD8-8D51-6E4EB08020DC}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EFD2C8B6-8B95-4915-A0C8-E9C9FD3157CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E2291D4-560B-4FD8-8D51-6E4EB08020DC}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EFD2C8B6-8B95-4915-A0C8-E9C9FD3157CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6317,10 +6314,10 @@
         <xdr:cNvPr id="79" name="Line 78">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73083669-1815-4E5A-A1C9-1145A227AF5C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8BC92A48-C993-4379-82C3-25E4BDADB5E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73083669-1815-4E5A-A1C9-1145A227AF5C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8BC92A48-C993-4379-82C3-25E4BDADB5E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6368,10 +6365,10 @@
         <xdr:cNvPr id="80" name="Line 79">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A660BC9-D5A0-407F-BE52-8864514F84B6}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45BE2D99-C00F-4D18-A21B-B2E120AD4FB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A660BC9-D5A0-407F-BE52-8864514F84B6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{45BE2D99-C00F-4D18-A21B-B2E120AD4FB6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6419,10 +6416,10 @@
         <xdr:cNvPr id="81" name="Line 80">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EA1B37A-D508-45D8-92D3-E938B3A734C6}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9D17F33E-124E-4728-A3C7-8BCF3A05D963}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EA1B37A-D508-45D8-92D3-E938B3A734C6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9D17F33E-124E-4728-A3C7-8BCF3A05D963}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6470,10 +6467,10 @@
         <xdr:cNvPr id="82" name="Line 81">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4BC24B-0B74-4396-98DD-A855B3BB2002}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EE4612AD-BF76-4756-B03A-050BAE9FD501}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4BC24B-0B74-4396-98DD-A855B3BB2002}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EE4612AD-BF76-4756-B03A-050BAE9FD501}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6521,10 +6518,10 @@
         <xdr:cNvPr id="83" name="Line 82">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91217C54-4B72-4735-8B73-2CDF3D249E29}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4622D68E-D08C-4652-B061-4ADB192CFF7F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91217C54-4B72-4735-8B73-2CDF3D249E29}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4622D68E-D08C-4652-B061-4ADB192CFF7F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6572,10 +6569,10 @@
         <xdr:cNvPr id="84" name="Line 83">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4786D163-12E0-4320-A3DC-A5AE34B34C32}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{84D726EE-F357-4D61-8E78-4F240976B1D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4786D163-12E0-4320-A3DC-A5AE34B34C32}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{84D726EE-F357-4D61-8E78-4F240976B1D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6623,10 +6620,10 @@
         <xdr:cNvPr id="85" name="Line 84">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{230958EB-1987-4429-8803-BD1376DD6D66}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6EDB26ED-361F-4CBD-9502-2948AD04C0B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{230958EB-1987-4429-8803-BD1376DD6D66}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6EDB26ED-361F-4CBD-9502-2948AD04C0B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6674,10 +6671,10 @@
         <xdr:cNvPr id="86" name="Line 85">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71B12B8-3068-491B-A69F-FF380DE81208}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E755E65A-1124-4FC3-B0CB-F74E5197B091}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71B12B8-3068-491B-A69F-FF380DE81208}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E755E65A-1124-4FC3-B0CB-F74E5197B091}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6725,10 +6722,10 @@
         <xdr:cNvPr id="87" name="Line 86">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B1E4608-AD49-4969-9A26-A6D2C1905F6A}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8047365C-A285-40E3-8733-A3AF6850A83B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B1E4608-AD49-4969-9A26-A6D2C1905F6A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8047365C-A285-40E3-8733-A3AF6850A83B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6776,10 +6773,10 @@
         <xdr:cNvPr id="88" name="Line 87">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA18065-0A8A-48F3-9256-5637BA69FE19}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BE79E203-6901-4C61-A0A3-6C663A8B4F6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA18065-0A8A-48F3-9256-5637BA69FE19}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BE79E203-6901-4C61-A0A3-6C663A8B4F6F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6827,10 +6824,10 @@
         <xdr:cNvPr id="89" name="Line 88">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41BB73F0-9310-4C14-9482-35BD5D141A41}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D342E331-9BAC-44A6-9FB8-26B2534184BE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41BB73F0-9310-4C14-9482-35BD5D141A41}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D342E331-9BAC-44A6-9FB8-26B2534184BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6878,10 +6875,10 @@
         <xdr:cNvPr id="90" name="Line 89">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B74F76-51C0-4CAD-A3E4-6A73E3059D97}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{889DDC7C-FE6C-4B88-8B19-5DECE7B30BC5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B74F76-51C0-4CAD-A3E4-6A73E3059D97}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{889DDC7C-FE6C-4B88-8B19-5DECE7B30BC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6929,10 +6926,10 @@
         <xdr:cNvPr id="91" name="Line 90">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0975AAB9-C191-4F1B-9E1B-B9FBEA0BAC9D}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{799BA03E-D4CC-4761-8E23-F58F524E9656}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0975AAB9-C191-4F1B-9E1B-B9FBEA0BAC9D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{799BA03E-D4CC-4761-8E23-F58F524E9656}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6980,10 +6977,10 @@
         <xdr:cNvPr id="92" name="Line 91">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A31BA120-8E6D-47C6-B43D-25FCE996C8BF}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EBC088CD-1037-46C9-93A9-E52FBE0013E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A31BA120-8E6D-47C6-B43D-25FCE996C8BF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EBC088CD-1037-46C9-93A9-E52FBE0013E7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7031,10 +7028,10 @@
         <xdr:cNvPr id="93" name="Line 92">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{015DE011-4C5A-4506-A1FC-73FCF80DA8F3}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7E0FB1D1-999B-43D2-991A-280B6F8312F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{015DE011-4C5A-4506-A1FC-73FCF80DA8F3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7E0FB1D1-999B-43D2-991A-280B6F8312F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7082,10 +7079,10 @@
         <xdr:cNvPr id="94" name="Line 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1469B199-5D37-46AE-B10E-50FF045D6081}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5EDDDE38-7427-46C2-885D-CF14011933D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1469B199-5D37-46AE-B10E-50FF045D6081}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{5EDDDE38-7427-46C2-885D-CF14011933D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7133,10 +7130,10 @@
         <xdr:cNvPr id="95" name="Line 94">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3AECB4E-2730-4AE5-BD8D-0C9EF17D981C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F78BC497-644B-4231-8440-3732AB29CF80}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3AECB4E-2730-4AE5-BD8D-0C9EF17D981C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{F78BC497-644B-4231-8440-3732AB29CF80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7184,10 +7181,10 @@
         <xdr:cNvPr id="96" name="Line 95">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADA67C4D-007C-473A-AF33-4154B9E0CE8F}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B3BE0842-0752-49AF-8396-FDAFEE145A0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADA67C4D-007C-473A-AF33-4154B9E0CE8F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B3BE0842-0752-49AF-8396-FDAFEE145A0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7235,10 +7232,10 @@
         <xdr:cNvPr id="97" name="Line 96">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D44E83C-6063-4CBA-89AB-4FC776AC2B09}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{79714EC5-9D6B-4863-B094-F993D55A808C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D44E83C-6063-4CBA-89AB-4FC776AC2B09}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{79714EC5-9D6B-4863-B094-F993D55A808C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7286,10 +7283,10 @@
         <xdr:cNvPr id="98" name="Line 97">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDE6F47-9376-4B0E-BC7C-0EB623111BD9}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1D781A6E-BD1A-49C0-A9E1-DB9F9AA84A84}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDE6F47-9376-4B0E-BC7C-0EB623111BD9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1D781A6E-BD1A-49C0-A9E1-DB9F9AA84A84}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7337,10 +7334,10 @@
         <xdr:cNvPr id="99" name="Line 98">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4312836B-6BD2-46F0-84E9-ED49171329F1}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A4D88ADD-E1B5-4BE8-A540-BE79ABFF9523}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4312836B-6BD2-46F0-84E9-ED49171329F1}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A4D88ADD-E1B5-4BE8-A540-BE79ABFF9523}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7388,10 +7385,10 @@
         <xdr:cNvPr id="100" name="Line 99">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD74307A-410E-4C05-8752-95363F6E54B7}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BEE49365-9298-43D1-BABD-E083F7811E32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD74307A-410E-4C05-8752-95363F6E54B7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BEE49365-9298-43D1-BABD-E083F7811E32}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7713,90 +7710,90 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L81"/>
-  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="4" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="6" customWidth="1"/>
     <col min="8" max="8" width="20" style="6" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" style="6" customWidth="1"/>
     <col min="11" max="11" width="20" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="15.6640625" style="6"/>
+    <col min="12" max="16384" width="15.7109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
-      <c r="H1" s="137" t="s">
+      <c r="H1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="139"/>
-      <c r="J1" s="141" t="s">
+      <c r="I1" s="58"/>
+      <c r="J1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="143"/>
+      <c r="K1" s="62"/>
     </row>
-    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="145" t="s">
+      <c r="D2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="144"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="63"/>
     </row>
-    <row r="3" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="147" t="s">
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="148"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="144"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="63"/>
     </row>
-    <row r="4" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="147" t="s">
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="150"/>
+      <c r="K4" s="69"/>
     </row>
-    <row r="5" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
       <c r="C5" s="9"/>
       <c r="D5" s="10"/>
@@ -7807,76 +7804,76 @@
         <v>5</v>
       </c>
       <c r="I5" s="14"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="151"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="70"/>
     </row>
-    <row r="6" spans="2:11" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="14.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
-      <c r="C6" s="131" t="s">
+      <c r="C6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-      <c r="K6" s="134"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="53"/>
     </row>
-    <row r="7" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="136"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
     </row>
-    <row r="8" spans="2:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="12.75" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
       <c r="C8" s="15"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="125"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="73"/>
     </row>
-    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
       <c r="C9" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="128" t="s">
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="130"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="78"/>
     </row>
-    <row r="10" spans="2:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="12.75" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
       <c r="C10" s="19"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="113"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="81"/>
     </row>
-    <row r="11" spans="2:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="12.75" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
       <c r="C11" s="22" t="s">
         <v>8</v>
@@ -7884,25 +7881,25 @@
       <c r="D11" s="23"/>
       <c r="E11" s="24"/>
       <c r="F11" s="25"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="113"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="81"/>
     </row>
-    <row r="12" spans="2:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="12.75" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
       <c r="C12" s="19"/>
       <c r="D12" s="20"/>
       <c r="E12" s="26"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
-      <c r="K12" s="113"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="81"/>
     </row>
-    <row r="13" spans="2:11" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="12.75" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
       <c r="C13" s="22" t="s">
         <v>9</v>
@@ -7910,928 +7907,969 @@
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="113"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="81"/>
     </row>
-    <row r="14" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="27"/>
       <c r="D14" s="28"/>
       <c r="E14" s="29"/>
       <c r="F14" s="30"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="116"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="84"/>
     </row>
-    <row r="15" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="120" t="s">
+      <c r="H15" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="122"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="90"/>
     </row>
-    <row r="16" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="93" t="s">
+    <row r="16" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="110"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="99"/>
     </row>
-    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="94"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="86"/>
+    <row r="17" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="92"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="101"/>
+      <c r="J17" s="101"/>
+      <c r="K17" s="102"/>
     </row>
-    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="94"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="35"/>
+    <row r="18" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="92"/>
+      <c r="C18" s="109"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="101"/>
+      <c r="J18" s="101"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="32"/>
     </row>
-    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="94"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="92"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="85"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="36"/>
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="92"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="101"/>
+      <c r="J19" s="101"/>
+      <c r="K19" s="102"/>
+      <c r="L19" s="33"/>
     </row>
-    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="94"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="92"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="36"/>
+    <row r="20" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="92"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="101"/>
+      <c r="J20" s="101"/>
+      <c r="K20" s="102"/>
+      <c r="L20" s="33"/>
     </row>
-    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="94"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="36"/>
+    <row r="21" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="92"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="102"/>
+      <c r="L21" s="33"/>
     </row>
-    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="94"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="36"/>
+    <row r="22" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="92"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="102"/>
+      <c r="L22" s="33"/>
     </row>
-    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="94"/>
-      <c r="C23" s="90"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="36"/>
+    <row r="23" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="92"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="33"/>
     </row>
-    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="94"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="36"/>
+    <row r="24" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="92"/>
+      <c r="C24" s="109"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="33"/>
     </row>
-    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="94"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="36"/>
+    <row r="25" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="92"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="101"/>
+      <c r="K25" s="102"/>
+      <c r="L25" s="33"/>
     </row>
-    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="94"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="35"/>
+    <row r="26" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="92"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="95"/>
+      <c r="H26" s="100"/>
+      <c r="I26" s="101"/>
+      <c r="J26" s="101"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="32"/>
     </row>
-    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="94"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="35"/>
+    <row r="27" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="92"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="100"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
+      <c r="K27" s="102"/>
+      <c r="L27" s="32"/>
     </row>
-    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="94"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="85"/>
-      <c r="J28" s="85"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="36"/>
+    <row r="28" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="92"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="95"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
+      <c r="K28" s="102"/>
+      <c r="L28" s="33"/>
     </row>
-    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="94"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="91"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="35"/>
+    <row r="29" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="92"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="111"/>
+      <c r="G29" s="95"/>
+      <c r="H29" s="100"/>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="32"/>
     </row>
-    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="94"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="35"/>
+    <row r="30" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="92"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="32"/>
     </row>
-    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="94"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="35"/>
+    <row r="31" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="92"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="32"/>
     </row>
-    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="94"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="35"/>
+    <row r="32" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="92"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="95"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="32"/>
     </row>
-    <row r="33" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="94"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="84"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="35"/>
+    <row r="33" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="92"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="102"/>
+      <c r="L33" s="32"/>
     </row>
-    <row r="34" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="94"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="85"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="35"/>
+    <row r="34" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="92"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="95"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="101"/>
+      <c r="J34" s="101"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="32"/>
     </row>
-    <row r="35" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="94"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="85"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="35"/>
+    <row r="35" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="92"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="101"/>
+      <c r="J35" s="101"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="32"/>
     </row>
-    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="94"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92"/>
-      <c r="G36" s="106"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="85"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="35"/>
+    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="92"/>
+      <c r="C36" s="109"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="32"/>
     </row>
-    <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="94"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="85"/>
-      <c r="K37" s="86"/>
-      <c r="L37" s="35"/>
+    <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="92"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="111"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="102"/>
+      <c r="L37" s="32"/>
     </row>
-    <row r="38" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="94"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="92"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="35"/>
+    <row r="38" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="92"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="111"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="101"/>
+      <c r="J38" s="101"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="32"/>
     </row>
-    <row r="39" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="94"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="106"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="36"/>
+    <row r="39" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="92"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="110"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="101"/>
+      <c r="J39" s="101"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="33"/>
     </row>
-    <row r="40" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="94"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="106"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="36"/>
+    <row r="40" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="92"/>
+      <c r="C40" s="109"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="101"/>
+      <c r="J40" s="101"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="33"/>
     </row>
-    <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="94"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="36"/>
+    <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="92"/>
+      <c r="C41" s="109"/>
+      <c r="D41" s="110"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="111"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="101"/>
+      <c r="J41" s="101"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="33"/>
     </row>
-    <row r="42" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="94"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="106"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="85"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="36"/>
+    <row r="42" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="92"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="111"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="101"/>
+      <c r="J42" s="101"/>
+      <c r="K42" s="102"/>
+      <c r="L42" s="33"/>
     </row>
-    <row r="43" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="94"/>
-      <c r="C43" s="90"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="92"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="86"/>
-      <c r="L43" s="36"/>
+    <row r="43" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="92"/>
+      <c r="C43" s="109"/>
+      <c r="D43" s="110"/>
+      <c r="E43" s="110"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="33"/>
     </row>
-    <row r="44" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="94"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="92"/>
-      <c r="G44" s="106"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="85"/>
-      <c r="J44" s="85"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="35"/>
+    <row r="44" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="92"/>
+      <c r="C44" s="109"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="95"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="101"/>
+      <c r="J44" s="101"/>
+      <c r="K44" s="102"/>
+      <c r="L44" s="32"/>
     </row>
-    <row r="45" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="94"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="92"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="86"/>
-      <c r="L45" s="35"/>
+    <row r="45" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="92"/>
+      <c r="C45" s="109"/>
+      <c r="D45" s="110"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="111"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="100"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="102"/>
+      <c r="L45" s="32"/>
     </row>
-    <row r="46" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="94"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="91"/>
-      <c r="F46" s="92"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="84"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="85"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="36"/>
+    <row r="46" spans="2:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="92"/>
+      <c r="C46" s="109"/>
+      <c r="D46" s="110"/>
+      <c r="E46" s="110"/>
+      <c r="F46" s="111"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="100"/>
+      <c r="I46" s="101"/>
+      <c r="J46" s="101"/>
+      <c r="K46" s="102"/>
+      <c r="L46" s="33"/>
     </row>
-    <row r="47" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="94"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="91"/>
-      <c r="F47" s="92"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="86"/>
-      <c r="L47" s="36"/>
+    <row r="47" spans="2:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="92"/>
+      <c r="C47" s="109"/>
+      <c r="D47" s="110"/>
+      <c r="E47" s="110"/>
+      <c r="F47" s="111"/>
+      <c r="G47" s="95"/>
+      <c r="H47" s="100"/>
+      <c r="I47" s="101"/>
+      <c r="J47" s="101"/>
+      <c r="K47" s="102"/>
+      <c r="L47" s="33"/>
     </row>
-    <row r="48" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="94"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="91"/>
-      <c r="E48" s="91"/>
-      <c r="F48" s="92"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="84"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
-      <c r="K48" s="86"/>
-      <c r="L48" s="36"/>
+    <row r="48" spans="2:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="92"/>
+      <c r="C48" s="109"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="111"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="101"/>
+      <c r="J48" s="101"/>
+      <c r="K48" s="102"/>
+      <c r="L48" s="33"/>
     </row>
-    <row r="49" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="95"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="104"/>
-      <c r="G49" s="107"/>
-      <c r="H49" s="84"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="36"/>
+    <row r="49" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="93"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="113"/>
+      <c r="E49" s="113"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="100"/>
+      <c r="I49" s="101"/>
+      <c r="J49" s="101"/>
+      <c r="K49" s="102"/>
+      <c r="L49" s="33"/>
     </row>
-    <row r="50" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="94" t="s">
+    <row r="50" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="87"/>
-      <c r="D50" s="88"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="96"/>
-      <c r="H50" s="84"/>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="36"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="107"/>
+      <c r="E50" s="107"/>
+      <c r="F50" s="108"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="100"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="101"/>
+      <c r="K50" s="102"/>
+      <c r="L50" s="33"/>
     </row>
-    <row r="51" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="94"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="91"/>
-      <c r="E51" s="91"/>
-      <c r="F51" s="92"/>
-      <c r="G51" s="97"/>
-      <c r="H51" s="84"/>
-      <c r="I51" s="85"/>
-      <c r="J51" s="85"/>
-      <c r="K51" s="86"/>
-      <c r="L51" s="36"/>
+    <row r="51" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="92"/>
+      <c r="C51" s="109"/>
+      <c r="D51" s="110"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="104"/>
+      <c r="H51" s="100"/>
+      <c r="I51" s="101"/>
+      <c r="J51" s="101"/>
+      <c r="K51" s="102"/>
+      <c r="L51" s="33"/>
     </row>
-    <row r="52" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="94"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="91"/>
-      <c r="F52" s="92"/>
-      <c r="G52" s="97"/>
-      <c r="H52" s="84"/>
-      <c r="I52" s="85"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="86"/>
-      <c r="L52" s="36"/>
+    <row r="52" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="92"/>
+      <c r="C52" s="109"/>
+      <c r="D52" s="110"/>
+      <c r="E52" s="110"/>
+      <c r="F52" s="111"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="100"/>
+      <c r="I52" s="101"/>
+      <c r="J52" s="101"/>
+      <c r="K52" s="102"/>
+      <c r="L52" s="33"/>
     </row>
-    <row r="53" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="94"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="91"/>
-      <c r="E53" s="91"/>
-      <c r="F53" s="92"/>
-      <c r="G53" s="97"/>
-      <c r="H53" s="84"/>
-      <c r="I53" s="85"/>
-      <c r="J53" s="85"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="36"/>
+    <row r="53" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="92"/>
+      <c r="C53" s="109"/>
+      <c r="D53" s="110"/>
+      <c r="E53" s="110"/>
+      <c r="F53" s="111"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="101"/>
+      <c r="K53" s="102"/>
+      <c r="L53" s="33"/>
     </row>
-    <row r="54" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="94"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="91"/>
-      <c r="E54" s="91"/>
-      <c r="F54" s="92"/>
-      <c r="G54" s="97"/>
-      <c r="H54" s="84"/>
-      <c r="I54" s="85"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="86"/>
-      <c r="L54" s="36"/>
+    <row r="54" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="92"/>
+      <c r="C54" s="109"/>
+      <c r="D54" s="110"/>
+      <c r="E54" s="110"/>
+      <c r="F54" s="111"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="100"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="101"/>
+      <c r="K54" s="102"/>
+      <c r="L54" s="33"/>
     </row>
-    <row r="55" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="94"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="91"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="97"/>
-      <c r="H55" s="84"/>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="86"/>
-      <c r="L55" s="36"/>
+    <row r="55" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="92"/>
+      <c r="C55" s="109"/>
+      <c r="D55" s="110"/>
+      <c r="E55" s="110"/>
+      <c r="F55" s="111"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="100"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="101"/>
+      <c r="K55" s="102"/>
+      <c r="L55" s="33"/>
     </row>
-    <row r="56" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="94"/>
-      <c r="C56" s="90"/>
-      <c r="D56" s="91"/>
-      <c r="E56" s="91"/>
-      <c r="F56" s="92"/>
-      <c r="G56" s="97"/>
-      <c r="H56" s="84"/>
-      <c r="I56" s="85"/>
-      <c r="J56" s="85"/>
-      <c r="K56" s="86"/>
-      <c r="L56" s="36"/>
+    <row r="56" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="92"/>
+      <c r="C56" s="109"/>
+      <c r="D56" s="110"/>
+      <c r="E56" s="110"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="100"/>
+      <c r="I56" s="101"/>
+      <c r="J56" s="101"/>
+      <c r="K56" s="102"/>
+      <c r="L56" s="33"/>
     </row>
-    <row r="57" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="94"/>
-      <c r="C57" s="90"/>
-      <c r="D57" s="91"/>
-      <c r="E57" s="91"/>
-      <c r="F57" s="92"/>
-      <c r="G57" s="97"/>
-      <c r="H57" s="84"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="36"/>
+    <row r="57" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="92"/>
+      <c r="C57" s="109"/>
+      <c r="D57" s="110"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="100"/>
+      <c r="I57" s="101"/>
+      <c r="J57" s="101"/>
+      <c r="K57" s="102"/>
+      <c r="L57" s="33"/>
     </row>
-    <row r="58" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="94"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="91"/>
-      <c r="E58" s="91"/>
-      <c r="F58" s="92"/>
-      <c r="G58" s="97"/>
-      <c r="H58" s="84"/>
-      <c r="I58" s="85"/>
-      <c r="J58" s="85"/>
-      <c r="K58" s="86"/>
-      <c r="L58" s="36"/>
+    <row r="58" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="92"/>
+      <c r="C58" s="109"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="110"/>
+      <c r="F58" s="111"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="100"/>
+      <c r="I58" s="101"/>
+      <c r="J58" s="101"/>
+      <c r="K58" s="102"/>
+      <c r="L58" s="33"/>
     </row>
-    <row r="59" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="94"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="91"/>
-      <c r="E59" s="91"/>
-      <c r="F59" s="92"/>
-      <c r="G59" s="97"/>
-      <c r="H59" s="84"/>
-      <c r="I59" s="85"/>
-      <c r="J59" s="85"/>
-      <c r="K59" s="86"/>
-      <c r="L59" s="36"/>
+    <row r="59" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="92"/>
+      <c r="C59" s="109"/>
+      <c r="D59" s="110"/>
+      <c r="E59" s="110"/>
+      <c r="F59" s="111"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="100"/>
+      <c r="I59" s="101"/>
+      <c r="J59" s="101"/>
+      <c r="K59" s="102"/>
+      <c r="L59" s="33"/>
     </row>
-    <row r="60" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="94"/>
-      <c r="C60" s="90"/>
-      <c r="D60" s="91"/>
-      <c r="E60" s="91"/>
-      <c r="F60" s="92"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="84"/>
-      <c r="I60" s="85"/>
-      <c r="J60" s="85"/>
-      <c r="K60" s="86"/>
-      <c r="L60" s="36"/>
+    <row r="60" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="92"/>
+      <c r="C60" s="109"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="100"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="102"/>
+      <c r="L60" s="33"/>
     </row>
-    <row r="61" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="95"/>
-      <c r="C61" s="90"/>
-      <c r="D61" s="91"/>
-      <c r="E61" s="91"/>
-      <c r="F61" s="92"/>
-      <c r="G61" s="98"/>
-      <c r="H61" s="84"/>
-      <c r="I61" s="85"/>
-      <c r="J61" s="85"/>
-      <c r="K61" s="86"/>
-      <c r="L61" s="36"/>
+    <row r="61" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="93"/>
+      <c r="C61" s="109"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="111"/>
+      <c r="G61" s="105"/>
+      <c r="H61" s="100"/>
+      <c r="I61" s="101"/>
+      <c r="J61" s="101"/>
+      <c r="K61" s="102"/>
+      <c r="L61" s="33"/>
     </row>
-    <row r="62" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="93" t="s">
+    <row r="62" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="87"/>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="96"/>
-      <c r="H62" s="84"/>
-      <c r="I62" s="85"/>
-      <c r="J62" s="85"/>
-      <c r="K62" s="86"/>
-      <c r="L62" s="36"/>
+      <c r="C62" s="106"/>
+      <c r="D62" s="107"/>
+      <c r="E62" s="107"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="100"/>
+      <c r="I62" s="101"/>
+      <c r="J62" s="101"/>
+      <c r="K62" s="102"/>
+      <c r="L62" s="33"/>
     </row>
-    <row r="63" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="94"/>
-      <c r="C63" s="90"/>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
-      <c r="F63" s="92"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="84"/>
-      <c r="I63" s="85"/>
-      <c r="J63" s="85"/>
-      <c r="K63" s="86"/>
-      <c r="L63" s="36"/>
+    <row r="63" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="92"/>
+      <c r="C63" s="109"/>
+      <c r="D63" s="110"/>
+      <c r="E63" s="110"/>
+      <c r="F63" s="111"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="100"/>
+      <c r="I63" s="101"/>
+      <c r="J63" s="101"/>
+      <c r="K63" s="102"/>
+      <c r="L63" s="33"/>
     </row>
-    <row r="64" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="94"/>
-      <c r="C64" s="90"/>
-      <c r="D64" s="91"/>
-      <c r="E64" s="91"/>
-      <c r="F64" s="92"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="84"/>
-      <c r="I64" s="85"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="86"/>
-      <c r="L64" s="36"/>
+    <row r="64" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="92"/>
+      <c r="C64" s="109"/>
+      <c r="D64" s="110"/>
+      <c r="E64" s="110"/>
+      <c r="F64" s="111"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="100"/>
+      <c r="I64" s="101"/>
+      <c r="J64" s="101"/>
+      <c r="K64" s="102"/>
+      <c r="L64" s="33"/>
     </row>
-    <row r="65" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="94"/>
-      <c r="C65" s="90"/>
-      <c r="D65" s="91"/>
-      <c r="E65" s="91"/>
-      <c r="F65" s="92"/>
-      <c r="G65" s="97"/>
-      <c r="H65" s="84"/>
-      <c r="I65" s="85"/>
-      <c r="J65" s="85"/>
-      <c r="K65" s="86"/>
-      <c r="L65" s="36"/>
+    <row r="65" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="92"/>
+      <c r="C65" s="109"/>
+      <c r="D65" s="110"/>
+      <c r="E65" s="110"/>
+      <c r="F65" s="111"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="100"/>
+      <c r="I65" s="101"/>
+      <c r="J65" s="101"/>
+      <c r="K65" s="102"/>
+      <c r="L65" s="33"/>
     </row>
-    <row r="66" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="94"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="91"/>
-      <c r="E66" s="91"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="97"/>
-      <c r="H66" s="84"/>
-      <c r="I66" s="85"/>
-      <c r="J66" s="85"/>
-      <c r="K66" s="86"/>
-      <c r="L66" s="36"/>
+    <row r="66" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="92"/>
+      <c r="C66" s="109"/>
+      <c r="D66" s="110"/>
+      <c r="E66" s="110"/>
+      <c r="F66" s="111"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="100"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="101"/>
+      <c r="K66" s="102"/>
+      <c r="L66" s="33"/>
     </row>
-    <row r="67" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="94"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="91"/>
-      <c r="E67" s="91"/>
-      <c r="F67" s="92"/>
-      <c r="G67" s="97"/>
-      <c r="H67" s="84"/>
-      <c r="I67" s="85"/>
-      <c r="J67" s="85"/>
-      <c r="K67" s="86"/>
+    <row r="67" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="92"/>
+      <c r="C67" s="109"/>
+      <c r="D67" s="110"/>
+      <c r="E67" s="110"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="100"/>
+      <c r="I67" s="101"/>
+      <c r="J67" s="101"/>
+      <c r="K67" s="102"/>
     </row>
-    <row r="68" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="95"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="91"/>
-      <c r="E68" s="91"/>
-      <c r="F68" s="92"/>
-      <c r="G68" s="98"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="100"/>
-      <c r="J68" s="100"/>
-      <c r="K68" s="101"/>
+    <row r="68" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="93"/>
+      <c r="C68" s="109"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="110"/>
+      <c r="F68" s="111"/>
+      <c r="G68" s="105"/>
+      <c r="H68" s="115"/>
+      <c r="I68" s="116"/>
+      <c r="J68" s="116"/>
+      <c r="K68" s="117"/>
     </row>
-    <row r="69" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="1"/>
-      <c r="C69" s="56" t="s">
+      <c r="C69" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="D69" s="57"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="37" t="s">
+      <c r="D69" s="119"/>
+      <c r="E69" s="120"/>
+      <c r="F69" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G69" s="64"/>
-      <c r="H69" s="65"/>
-      <c r="I69" s="37" t="s">
+      <c r="G69" s="121"/>
+      <c r="H69" s="122"/>
+      <c r="I69" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="J69" s="66"/>
-      <c r="K69" s="67"/>
+      <c r="J69" s="123"/>
+      <c r="K69" s="124"/>
     </row>
-    <row r="70" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="7"/>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="68" t="s">
+      <c r="D70" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="E70" s="69"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="39"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="41"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="36"/>
+      <c r="J70" s="37"/>
+      <c r="K70" s="38"/>
     </row>
-    <row r="71" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
-      <c r="C71" s="42"/>
-      <c r="D71" s="70"/>
-      <c r="E71" s="71"/>
-      <c r="F71" s="43" t="s">
+      <c r="C71" s="39"/>
+      <c r="D71" s="127"/>
+      <c r="E71" s="128"/>
+      <c r="F71" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="G71" s="74"/>
-      <c r="H71" s="75"/>
-      <c r="I71" s="43" t="s">
+      <c r="G71" s="131"/>
+      <c r="H71" s="132"/>
+      <c r="I71" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="J71" s="72"/>
-      <c r="K71" s="73"/>
+      <c r="J71" s="129"/>
+      <c r="K71" s="130"/>
     </row>
-    <row r="72" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
-      <c r="C72" s="56" t="s">
+      <c r="C72" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="57"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="39"/>
-      <c r="J72" s="40"/>
-      <c r="K72" s="41"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="120"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="37"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="37"/>
+      <c r="K72" s="38"/>
     </row>
-    <row r="73" spans="2:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="7"/>
-      <c r="C73" s="44" t="s">
+      <c r="C73" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D73" s="76" t="s">
+      <c r="D73" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="E73" s="77"/>
-      <c r="F73" s="43" t="s">
+      <c r="E73" s="134"/>
+      <c r="F73" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="78"/>
-      <c r="H73" s="79"/>
-      <c r="I73" s="43" t="s">
+      <c r="G73" s="135"/>
+      <c r="H73" s="136"/>
+      <c r="I73" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="J73" s="80" t="s">
+      <c r="J73" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="81"/>
+      <c r="K73" s="138"/>
     </row>
-    <row r="74" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="45"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="45"/>
+    <row r="74" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="42"/>
+      <c r="C74" s="43"/>
+      <c r="D74" s="139"/>
+      <c r="E74" s="140"/>
+      <c r="F74" s="42"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="7"/>
       <c r="J74" s="11"/>
-      <c r="K74" s="47"/>
+      <c r="K74" s="44"/>
     </row>
-    <row r="75" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="45"/>
-      <c r="C75" s="56" t="s">
+    <row r="75" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="42"/>
+      <c r="C75" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="D75" s="57"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="45"/>
+      <c r="D75" s="119"/>
+      <c r="E75" s="120"/>
+      <c r="F75" s="42"/>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
       <c r="I75" s="7"/>
       <c r="J75" s="11"/>
-      <c r="K75" s="47"/>
+      <c r="K75" s="44"/>
     </row>
-    <row r="76" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="45"/>
-      <c r="C76" s="53"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="45"/>
+    <row r="76" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="42"/>
+      <c r="C76" s="141"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="143"/>
+      <c r="F76" s="42"/>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
       <c r="I76" s="7"/>
       <c r="J76" s="11"/>
-      <c r="K76" s="47"/>
+      <c r="K76" s="44"/>
     </row>
-    <row r="77" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7"/>
-      <c r="C77" s="56" t="s">
+      <c r="C77" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="D77" s="57"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="43" t="s">
+      <c r="D77" s="119"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="G77" s="59" t="s">
+      <c r="G77" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="H77" s="60"/>
-      <c r="I77" s="43" t="s">
+      <c r="H77" s="145"/>
+      <c r="I77" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="J77" s="59" t="s">
+      <c r="J77" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="K77" s="60"/>
+      <c r="K77" s="145"/>
     </row>
-    <row r="78" spans="2:12" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="48"/>
-      <c r="C78" s="61">
+    <row r="78" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="45"/>
+      <c r="C78" s="146">
         <f>(D74-C74)+C71+D71</f>
         <v>0</v>
       </c>
-      <c r="D78" s="62"/>
-      <c r="E78" s="63"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="51"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="50"/>
-      <c r="K78" s="51"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="148"/>
+      <c r="F78" s="46"/>
+      <c r="G78" s="47"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="47"/>
+      <c r="K78" s="48"/>
     </row>
-    <row r="80" spans="2:12" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
+    <row r="80" spans="2:12" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
     </row>
-    <row r="81" spans="3:5" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="C81" s="52"/>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
+    <row r="81" spans="3:5" ht="12.75" x14ac:dyDescent="0.25">
+      <c r="C81" s="49"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:K7"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="H15:K15"/>
+  <mergeCells count="103">
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="H57:K57"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="C50:F61"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="B62:B68"/>
+    <mergeCell ref="G62:G68"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="H64:K64"/>
+    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="H67:K67"/>
+    <mergeCell ref="H68:K68"/>
+    <mergeCell ref="C62:F68"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="B50:B61"/>
+    <mergeCell ref="G50:G61"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H59:K59"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="C16:F49"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H40:K40"/>
     <mergeCell ref="B16:B49"/>
     <mergeCell ref="G16:G49"/>
     <mergeCell ref="H16:K16"/>
@@ -8848,67 +8886,29 @@
     <mergeCell ref="H20:K20"/>
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="H22:K22"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H49:K49"/>
-    <mergeCell ref="B50:B61"/>
-    <mergeCell ref="G50:G61"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H59:K59"/>
-    <mergeCell ref="H60:K60"/>
-    <mergeCell ref="H61:K61"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="C16:F49"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="B62:B68"/>
-    <mergeCell ref="G62:G68"/>
-    <mergeCell ref="H62:K62"/>
-    <mergeCell ref="H63:K63"/>
-    <mergeCell ref="H64:K64"/>
-    <mergeCell ref="H65:K65"/>
-    <mergeCell ref="H66:K66"/>
-    <mergeCell ref="H67:K67"/>
-    <mergeCell ref="H68:K68"/>
-    <mergeCell ref="C62:F68"/>
-    <mergeCell ref="H57:K57"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="C50:F61"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="J71:K71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:K7"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
